--- a/daily_matches/job_matches_2026-04-15.xlsx
+++ b/daily_matches/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b4467c3c6aa55</t>
+          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend Engineer II</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, Kafka, PostgreSQL, MySQL, NoSQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2342b890625b11</t>
+          <t>https://www.indeed.com/viewjob?jk=6858ebe4d9bc0b8b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, FastAPI, Docker, Kubernetes, Terraform, Git, Kafka, Python</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, FastAPI, Snowflake, Databricks, Kafka, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,137 +566,137 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd17ae9e035b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Banner Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b635a4480602f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Research Engineer II</t>
+          <t>Generative AI Healthcare Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Bacancy Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bryan, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, Data Lake, Jenkins, Hadoop, NoSQL, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b3207da19db4ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d04551ad1cdbf319</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer III, Machine Learning Software</t>
+          <t>Software Engineer Intern - Platform &amp; DevOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, XGBoost, S3, EC2, CI/CD, Git, Snowflake, Python, SQL</t>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e38b030f65d339e</t>
+          <t>https://www.indeed.com/viewjob?jk=44f9296e2dde0aa9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst Seniors: Cloud Engineering</t>
+          <t>Prompt Engineer, AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, AKS, CI/CD, Jenkins, Git, Databricks, PySpark, Python</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Prompt Engineering, Python, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d87aa04a7733264b</t>
+          <t>https://www.indeed.com/viewjob?jk=43ca1d9e93dfbc5f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist AI/ML</t>
+          <t>Applied AI ML, Senior Associate - Sales Science</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Copilot, TensorFlow, PyTorch, Git, Snowflake, Tableau, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde8a1217bb1b088</t>
+          <t>https://www.indeed.com/viewjob?jk=00164ad494631eaf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack React Developer | QE AI Efforts</t>
+          <t>Apprentice, Software Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Purchasing Platform</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FAISS, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,94 +776,94 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6b846e243ed35a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac86cc35b3bbfff</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack React Developer | QE AI Efforts</t>
+          <t>Software Engineer III - Python, AWS, GenAI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FAISS, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56bd7077100847ca</t>
+          <t>https://www.indeed.com/viewjob?jk=30f893c4214efe6c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Analyst - Technical - Senior</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, GitHub Actions, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+          <t>Redshift, Git, Snowflake, Redshift, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69713d6be44a4b67</t>
+          <t>https://www.indeed.com/viewjob?jk=1aa947fea0926418</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - GenAI (Teradyne, North Reading)</t>
+          <t>Software Engineer II - Athlete Care Technology (REMOTE)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,227 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Databricks, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83660e2bf37d59c8</t>
+          <t>https://www.indeed.com/viewjob?jk=613f7a3370987888</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Branch Channel Generative AI - Applied AI ML Senior Associate</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a30617048dc563e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Intern - Research</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45a978ac37e821a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Temporary Intern - AI Engineering</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, Hadoop, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4242686fdce96300</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Decision Science Analyst - Space &amp; Merchandising Analytics</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HEB</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Tableau, MicroStrategy, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74873ecd3638ec14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Product Security Engineer - Apps</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Universal Cable Holdings</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88968682d7cabadd</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Product Security Engineer - Applications</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Universal Cable Holdings</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0bc48dd03b1ec2c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-15.xlsx
+++ b/daily_matches/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,42 +486,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Prompt Engineering, Redshift, Apache Airflow, Git, Snowflake, Redshift, PostgreSQL, MySQL, MongoDB</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, spaCy, AWS SageMaker, Azure ML, Synapse, Apache Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560d14506d8aa36b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc13b56a1dadc810</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, spaCy, AWS SageMaker, Azure ML, Synapse, Apache Airflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6858ebe4d9bc0b8b</t>
+          <t>https://www.indeed.com/viewjob?jk=42cc0c644ae78852</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Dallas, TX</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, FastAPI, Snowflake, Databricks, Kafka, Python</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, spaCy, AWS SageMaker, Azure ML, Synapse, Apache Airflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865a46cfbc7cc3f4</t>
+          <t>https://www.indeed.com/viewjob?jk=46d19923987ef429</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banner Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Silicon Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, spaCy, AWS SageMaker, Azure ML, Synapse, Apache Airflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d9928392bc7529</t>
+          <t>https://www.indeed.com/viewjob?jk=fa06155bf991d0f8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Generative AI Healthcare Engineer</t>
+          <t>Deal Data Technology &amp; Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bacancy Technology</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Python</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, spaCy, AWS SageMaker, Azure ML, Synapse, Apache Airflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d04551ad1cdbf319</t>
+          <t>https://www.indeed.com/viewjob?jk=22e6ab66fd67032d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer Intern - Platform &amp; DevOps</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R</t>
+          <t>Data Scientist, TensorFlow, XGBoost, S3, Athena, Data Lake, FastAPI, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f9296e2dde0aa9</t>
+          <t>https://www.indeed.com/viewjob?jk=f99034f0e149e6e6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prompt Engineer, AI</t>
+          <t>Machine Learning Engineer (171680)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Prompt Engineering, Python, R, Scala, Optimization, A/B Testing</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,164 +706,164 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ca1d9e93dfbc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=a860d07867e70be2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applied AI ML, Senior Associate - Sales Science</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Optimization</t>
+          <t>Redshift, Git, Snowflake, Redshift, Kafka, Hadoop, MySQL, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00164ad494631eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=cb699a2e3bdbb440</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Apprentice, Software Engineering</t>
+          <t>Senior Data Scientist – Professional Tax Group (FP&amp;A)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Purchasing Platform</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac86cc35b3bbfff</t>
+          <t>https://www.indeed.com/viewjob?jk=c4150f7f15780a07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, AWS, GenAI</t>
+          <t>(Entry level) Full Stack Software Engineer (LLM application Development)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Docker, CI/CD, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f893c4214efe6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0c0bc9918adb56</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Analyst - Technical - Senior</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, Git, Snowflake, Redshift, Tableau, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aa947fea0926418</t>
+          <t>https://www.indeed.com/viewjob?jk=7bea47ac5f13bd1f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II - Athlete Care Technology (REMOTE)</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Ulteig</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Louis Park, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Databricks, Kafka, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613f7a3370987888</t>
+          <t>https://www.indeed.com/viewjob?jk=fdcb4c9fa82b59be</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Branch Channel Generative AI - Applied AI ML Senior Associate</t>
+          <t>Senior Software Engineer- Enrichment</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Optimization</t>
+          <t>LangChain, BigQuery, Docker, Git, BigQuery, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30617048dc563e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d65729ad13e08b2f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern - Research</t>
+          <t>Associate Cloud Platform Engineer – Azure &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>InvoiceCloud</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45a978ac37e821a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6e7612633c6b53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Temporary Intern - AI Engineering</t>
+          <t>GTM Engineer New</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>InvoiceCloud</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Prompt Engineering, Hadoop, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4242686fdce96300</t>
+          <t>https://www.indeed.com/viewjob?jk=71cc0677ab998764</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Decision Science Analyst - Space &amp; Merchandising Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Databricks, Tableau, MicroStrategy, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>Generative AI, RAG, Git, Snowflake, PostgreSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74873ecd3638ec14</t>
+          <t>https://www.indeed.com/viewjob?jk=675a9b682fc72f6b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Product Security Engineer - Apps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Universal Cable Holdings</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, Git, Snowflake, PostgreSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88968682d7cabadd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c8026496e940786</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Product Security Engineer - Applications</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Universal Cable Holdings</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,122 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, Git, Snowflake, PostgreSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0bc48dd03b1ec2c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3beecb89267a49b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Snowflake, PostgreSQL, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=656d1c14c0006f5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Snowflake, PostgreSQL, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bbe105af0a765589</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist II (ML Operations)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Medica Services Company LLC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebee47f987309774</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-15.xlsx
+++ b/daily_matches/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer/Data Scientist</t>
+          <t>AI/ML Engineering Intern (Summer 2026)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Poshmark</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Kafka</t>
+          <t>TensorFlow, PyTorch, Redshift, MLflow, FastAPI, Docker, Kubernetes, Jenkins, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a711c2fcb36b6cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MacroHealth</t>
+          <t>Terminal Industries</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05733d6196b41ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad2f1b0e1a8289cb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GTM Systems Admin, Growth</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Python, SQL, R, Java, Scala</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,567 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=172c994a5d508b22</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tenet Advisors, LLC</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f47703eb8d2843d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Data Engineering Intern (Summer 2026)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Poshmark</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, Kinesis, Redshift, Kafka, Hadoop, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c56b117e10552e6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=538f15981f1af889</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Growth</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pomelo Care</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ce5843c62bdee4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Azure Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>innoVet Health, LLC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, Git, Databricks, PySpark, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Reliability Data Scientist III</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rheem Manufacturing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Roswell, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, MongoDB, Tableau, Power BI, Python, SQL, R, Scala, Bayesian, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82aab06ca0662bfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cloud Solution Architect</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Applied Information Sciences</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Kubernetes, GitHub Actions, Terraform, Git, Power BI, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4944bd9b2363edb</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Holland &amp; Knight</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brandon, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, AKS, MySQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec1771429282d515</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Front End Developer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Exiger</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=975a421ca329fcab</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Specialist - Architecture</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Supervisor, Software Engineering</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Energy Systems Group</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Newburgh, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Copilot, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Computer Vision &amp; Machine Learning Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tommy Car Wash</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0722b4c2c594e380</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer, Insider Risk - Global Security Organization</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f71fe61928b727f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Associate--Consumer Product Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Databricks, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5df7c12eedb2292</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Worldpay</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, CI/CD, Jenkins, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c2e9253a4f7ea74</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Worldpay</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, CI/CD, Jenkins, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f390b36bb24beae5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-15.xlsx
+++ b/daily_matches/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineering Intern (Summer 2026)</t>
+          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Redshift, MLflow, FastAPI, Docker, Kubernetes, Jenkins, Databricks, Redshift</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd3431b51acd4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=da8ab35096a74f07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr Data Scientist I</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Terminal Industries</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Dataflow, Hadoop, Tableau, Power BI, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad2f1b0e1a8289cb</t>
+          <t>https://www.indeed.com/viewjob?jk=62605a1609659e22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R</t>
+          <t>LangChain, RAG, Pinecone, ChromaDB, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4d88005315e7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47703eb8d2843d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d6412b42f521215b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineering Intern (Summer 2026)</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Poshmark</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, Kinesis, Redshift, Kafka, Hadoop, NoSQL, SQL, R, Java</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56b117e10552e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a467a1fe4bd409c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=538f15981f1af889</t>
+          <t>https://www.indeed.com/viewjob?jk=cea257394aa611a9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Growth</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pomelo Care</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R, A/B Testing</t>
+          <t>RAG, S3, Kinesis, Snowflake, Kafka, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce5843c62bdee4f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior AI Engineer (USA - Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Gurobi Optimization</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, Git, Databricks, PySpark, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, MLflow, Docker, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5acecf0e4305790</t>
+          <t>https://www.indeed.com/viewjob?jk=8490baf34f7648b7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reliability Data Scientist III</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rheem Manufacturing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, MongoDB, Tableau, Power BI, Python, SQL, R, Scala, Bayesian, A/B Testing</t>
+          <t>RAG, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82aab06ca0662bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, GitHub Actions, Terraform, Git, Power BI, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, XGBoost, AWS SageMaker, CI/CD, Git, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4944bd9b2363edb</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ccbb7af826ee21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Holland &amp; Knight</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brandon, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abb3ed211255b11</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Front End Developer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975a421ca329fcab</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766f2f5e9a7201f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Supervisor, Software Engineering</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Energy Systems Group</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newburgh, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c197f77bdf171e6</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Computer Vision &amp; Machine Learning Developer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0722b4c2c594e380</t>
+          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer, Insider Risk - Global Security Organization</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f71fe61928b727f2</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate--Consumer Product Data Scientist</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WILLDAN GROUP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5df7c12eedb2292</t>
+          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>GenAI Applications Program Analyst - Senior SWE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, CI/CD, Jenkins, Databricks, Python, R, Scala</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,42 +1091,427 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2e9253a4f7ea74</t>
+          <t>https://www.indeed.com/viewjob?jk=ed7a611dbb12927a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>Cloudera Public Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Plano, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Kubernetes, Terraform, Git, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Cloud Security and Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Troutman Pepper Locke</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, Prompt Engineering, MLflow, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Axios</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cc7c77ccebea3c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Research Engineer, FlexOlmo</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>The Allen Institute for Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, spaCy, Docker, AKS, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=480d37c62c4098cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (JS/TS, AWS)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Low Associates</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>South Bend, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Associate AI Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c0cae80edebcce4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Analytics Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=accf39e2d7c36551</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Applied Scientist, Machine Learning</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>McAfee</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, PyTorch, XGBoost, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d1513689170be64</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist - Pro</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d010a44b96f43eb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Backend Engineer — Luna Platform (NASA Mission Cloud)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MRI Technologies</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>10</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MLflow, CI/CD, Jenkins, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f390b36bb24beae5</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, FastAPI, Kubernetes, CI/CD, Git, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=511f3fadb35f3bc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SAP iXp Intern - Software Developer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88b311dfc40ea33a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Engineer &amp; Marketing Automation Specialist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Allure Salon Suite Consulting LLC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Moosic, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab6fc2a560476063</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-15.xlsx
+++ b/daily_matches/job_matches_2026-04-15.xlsx
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Solution Architect, Enterprise - Eastern Time Zone</t>
+          <t>Databricks Data Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Git, Snowflake, Databricks</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, MLflow, CI/CD, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da8ab35096a74f07</t>
+          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Scientist I</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Sunbit, Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Dataflow, Hadoop, Tableau, Power BI, Matplotlib, Seaborn</t>
+          <t>Data Lake, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Kafka, MySQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62605a1609659e22</t>
+          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps &amp; AI Automation Engineer</t>
+          <t>Java Engineer - Workplace Services Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, ChromaDB, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6b296a0ce2f382</t>
+          <t>https://www.indeed.com/viewjob?jk=f89e8b376604268c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Snowflake, Databricks, Kafka, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6412b42f521215b</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Docker, CI/CD, Python, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a467a1fe4bd409c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc86602efbb6048b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI Full Stack Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea257394aa611a9</t>
+          <t>https://www.indeed.com/viewjob?jk=45352b37d09b3038</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Machine Learning Engineer (MLE)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, Snowflake, Kafka, Tableau, Power BI, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Kafka, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e93266a037e0c18</t>
+          <t>https://www.indeed.com/viewjob?jk=f4f2364f76afa834</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (USA - Remote)</t>
+          <t>Software Engineer I - Full Stack</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gurobi Optimization</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, MLflow, Docker, CI/CD, Python, R</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8490baf34f7648b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e317b1b40c2e7beb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Python, R</t>
+          <t>RAG, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20056a5b9ffca80</t>
+          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer - Senior Backend</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>FriendliAI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, XGBoost, AWS SageMaker, CI/CD, Git, Snowflake, Python, R</t>
+          <t>Generative AI, RAG, Hugging Face, FastAPI, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ccbb7af826ee21</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2216253f426b34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31dfca06d884ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9feb8448cb31787b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Kubernetes, MySQL, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1cb632eed3bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=0052c238f2b8a655</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Copilot, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec090a150db0c5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3621d86226ebeb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineer I – Power Apps Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe79bacd5e58f55</t>
+          <t>https://www.indeed.com/viewjob?jk=5593861fa4bfe0a9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineer I – Power Apps Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09282ebd98b3570</t>
+          <t>https://www.indeed.com/viewjob?jk=b8360114a4423ec6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineer I – Power Apps Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1d73f24fc01af9</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb8a40510ef81ca</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Software Engineer I – Power Apps Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WILLDAN GROUP</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e4150c94fe908c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9e6f97fd05db322b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GenAI Applications Program Analyst - Senior SWE</t>
+          <t>Software Engineer I – Power Apps Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed7a611dbb12927a</t>
+          <t>https://www.indeed.com/viewjob?jk=1382bc665c429373</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloudera Public Cloud Platform Engineer</t>
+          <t>Software Engineer I – Power Apps Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Kubernetes, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7428fbc9c89fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=400dd574c8b51fc3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Cloud Security and Infrastructure Engineer</t>
+          <t>Software Engineer I – Power Apps Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, Prompt Engineering, MLflow, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04325b074eb62665</t>
+          <t>https://www.indeed.com/viewjob?jk=9723c3ddfe70e0f3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer I – Power Apps Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Axios</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, MySQL, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc7c77ccebea3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=75765ae9ac03e4f6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Research Engineer, FlexOlmo</t>
+          <t>AL/ML Technical Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Allen Institute for Artificial Intelligence</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, spaCy, Docker, AKS, Python, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, PySpark, Python, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480d37c62c4098cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b42db1ff8517d44e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer (JS/TS, AWS)</t>
+          <t>Software Engineer – AI Agents</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Low Associates</t>
+          <t>FriendliAI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Kubernetes, Python, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45727b1c951a0e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=8129bd62a469de99</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Python, R, Optimization</t>
+          <t>AI Engineer, Gemini, Copilot, AKS, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0cae80edebcce4</t>
+          <t>https://www.indeed.com/viewjob?jk=39ebe0aefa7a96aa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Analytics Scientist</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Horizon Media, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accf39e2d7c36551</t>
+          <t>https://www.indeed.com/viewjob?jk=80c0a7beba55c0a2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Applied Scientist, Machine Learning</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, PyTorch, XGBoost, Git, Python, SQL, R, Optimization</t>
+          <t>Copilot, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1513689170be64</t>
+          <t>https://www.indeed.com/viewjob?jk=2cbd64a3ee40ea7c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist - Pro</t>
+          <t>Senior Software Engineer - Self Service Automation</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d010a44b96f43eb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e08a485e827da8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Backend Engineer — Luna Platform (NASA Mission Cloud)</t>
+          <t>Software Engineer II, Data Services</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MRI Technologies</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, FastAPI, Kubernetes, CI/CD, Git, BigQuery, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511f3fadb35f3bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=486537e97ea19770</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAP iXp Intern - Software Developer</t>
+          <t>Senior Software Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, Jenkins, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b311dfc40ea33a</t>
+          <t>https://www.indeed.com/viewjob?jk=196a32851cf8a2e9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Engineer &amp; Marketing Automation Specialist</t>
+          <t>Senior Data Scientist - Shopping Experience (Search)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Allure Salon Suite Consulting LLC</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Moosic, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6fc2a560476063</t>
+          <t>https://www.indeed.com/viewjob?jk=a3839fef38f76f7b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-15.xlsx
+++ b/daily_matches/job_matches_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Data Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,42 +486,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, MLflow, CI/CD, Databricks, Redshift</t>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, Pinecone, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce89a36f70a3941b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a7229d351ba823</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sunbit, Inc</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Lake, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Kafka, MySQL, MongoDB, Python</t>
+          <t>Generative AI, RAG, S3, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444a89356fbe315</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5a94e3ea76c9da</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Engineer - Workplace Services Engineering</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89e8b376604268c</t>
+          <t>https://www.indeed.com/viewjob?jk=31ca2baaf21560e8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst/Associate - New York</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>RingCentral</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Snowflake, Databricks, Kafka, Hadoop, Python, SQL</t>
+          <t>Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd43ffc6d7fda89</t>
+          <t>https://www.indeed.com/viewjob?jk=d58093accd3aa883</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI ML Engineer</t>
+          <t>Software Development Engineer 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Docker, CI/CD, Python, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc86602efbb6048b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2d34c4f246868fb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer</t>
+          <t>Ground Data Software Engineer - Mid-Career</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, S3, Dataflow, Kubernetes, Git, Hadoop, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45352b37d09b3038</t>
+          <t>https://www.indeed.com/viewjob?jk=7102020004fb286b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (MLE)</t>
+          <t>Managing Engineer (Java/Spring)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Kafka, Hadoop, Python, R</t>
+          <t>RAG, Copilot, Redshift, Git, Snowflake, Databricks, Redshift, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4f2364f76afa834</t>
+          <t>https://www.indeed.com/viewjob?jk=3c759f2901f8f28e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer I - Full Stack</t>
+          <t>Senior AI Agent Engineer - SDLC Optimization</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>LangChain, RAG, Prompt Engineering, FastAPI, CI/CD, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e317b1b40c2e7beb</t>
+          <t>https://www.indeed.com/viewjob?jk=e7149a07a4ae92f8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Software Development Engineer 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, PostgreSQL, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14f238cb8b8c5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4038857cbb874542</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer - Senior Backend</t>
+          <t>Research Engineer, FlexOlmo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FriendliAI</t>
+          <t>The Allen Institute for Artificial Intelligence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, FastAPI, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, spaCy, Docker, AKS, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2216253f426b34</t>
+          <t>https://www.indeed.com/viewjob?jk=a55f79b1d9ee9b79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9feb8448cb31787b</t>
+          <t>https://www.indeed.com/viewjob?jk=2be9ee403cf20f67</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, MySQL, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0052c238f2b8a655</t>
+          <t>https://www.indeed.com/viewjob?jk=156e5a4def2a4a5d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Digital Innovation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Saint Bernard, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Optimization</t>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3621d86226ebeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c42eaf2b5f971383</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer I – Power Apps Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>RAG, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,567 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5593861fa4bfe0a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Software Engineer I – Power Apps Developer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>HNTB Corporation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8360114a4423ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Engineer I – Power Apps Developer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>HNTB Corporation</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb8a40510ef81ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer I – Power Apps Developer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HNTB Corporation</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e6f97fd05db322b</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer I – Power Apps Developer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>HNTB Corporation</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1382bc665c429373</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer I – Power Apps Developer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>HNTB Corporation</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=400dd574c8b51fc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Software Engineer I – Power Apps Developer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>HNTB Corporation</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9723c3ddfe70e0f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer I – Power Apps Developer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HNTB Corporation</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75765ae9ac03e4f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AL/ML Technical Architect</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, PySpark, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b42db1ff8517d44e</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer – AI Agents</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>FriendliAI</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Kubernetes, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8129bd62a469de99</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Reef Capital Partners</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Lehi, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, Gemini, Copilot, AKS, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39ebe0aefa7a96aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Horizon Media, Inc.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80c0a7beba55c0a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>The New IEM, LLC</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Copilot, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cbd64a3ee40ea7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Self Service Automation</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e08a485e827da8</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Data Services</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=486537e97ea19770</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Computer Vision</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CLEAR</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, Jenkins, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=196a32851cf8a2e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Shopping Experience (Search)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3839fef38f76f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b2cdf5f4ac6a6c1a</t>
         </is>
       </c>
     </row>
